--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY163"/>
+  <dimension ref="A1:AY165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24314,6 +24314,256 @@
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>128062834</v>
+      </c>
+      <c r="B164" t="n">
+        <v>57770</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Källmyren nr, Klingermyren, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>488692</v>
+      </c>
+      <c r="R164" t="n">
+        <v>7009959</v>
+      </c>
+      <c r="S164" t="n">
+        <v>25</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Christian Romberg</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Christian Romberg</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>128062811</v>
+      </c>
+      <c r="B165" t="n">
+        <v>57508</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Källmyren nr, Klingermyren, Kyrkås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>488692</v>
+      </c>
+      <c r="R165" t="n">
+        <v>7009959</v>
+      </c>
+      <c r="S165" t="n">
+        <v>25</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Christian Romberg</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Christian Romberg</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24319,7 +24319,7 @@
         <v>128062834</v>
       </c>
       <c r="B164" t="n">
-        <v>57770</v>
+        <v>57776</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>128062811</v>
       </c>
       <c r="B165" t="n">
-        <v>57508</v>
+        <v>57514</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24319,7 +24319,7 @@
         <v>128062834</v>
       </c>
       <c r="B164" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24319,7 +24319,7 @@
         <v>128062834</v>
       </c>
       <c r="B164" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>128062811</v>
       </c>
       <c r="B165" t="n">
-        <v>57514</v>
+        <v>57526</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24319,7 +24319,7 @@
         <v>128062834</v>
       </c>
       <c r="B164" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>128062811</v>
       </c>
       <c r="B165" t="n">
-        <v>57526</v>
+        <v>57530</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24446,7 +24446,7 @@
         <v>128062811</v>
       </c>
       <c r="B165" t="n">
-        <v>57530</v>
+        <v>57557</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24446,7 +24446,7 @@
         <v>128062811</v>
       </c>
       <c r="B165" t="n">
-        <v>57557</v>
+        <v>57561</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 26155-2021 artfynd.xlsx
+++ b/artfynd/A 26155-2021 artfynd.xlsx
@@ -24446,7 +24446,7 @@
         <v>128062811</v>
       </c>
       <c r="B165" t="n">
-        <v>57561</v>
+        <v>57564</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
